--- a/artifacts/downloads/CP37/CHILIS_Delivery Codisys_Desarrollo.xlsx
+++ b/artifacts/downloads/CP37/CHILIS_Delivery Codisys_Desarrollo.xlsx
@@ -151,7 +151,7 @@
     <t>Tipo Menú</t>
   </si>
   <si>
-    <t>2026-09-10</t>
+    <t>2026-09-11</t>
   </si>
   <si>
     <t>A</t>
